--- a/Planilhas/login.xlsx
+++ b/Planilhas/login.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,17 @@
         <v>12122016</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Planilhas/login.xlsx
+++ b/Planilhas/login.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,17 +1193,6 @@
         <v>12122016</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
